--- a/AAII_Financials/Quarterly/SMG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SMG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>SMG</t>
   </si>
@@ -656,539 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44562</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44198</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1172100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1459500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>354400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>387300</v>
       </c>
-      <c r="G8" s="3">
-        <v>1188000</v>
-      </c>
       <c r="H8" s="3">
+        <v>1159300</v>
+      </c>
+      <c r="I8" s="3">
         <v>1389700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>366600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>414700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1202200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1525400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>410400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>374500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1118700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1531500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>526600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>493700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1186100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1678400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>566000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>737800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1609700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1828800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>748600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>890300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1492700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1382800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>365800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>497700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1170300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1189900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>298100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>433900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>994600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1013300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>221500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>376700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>973400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1084600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>207400</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>72400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>805000</v>
+      </c>
+      <c r="E9" s="3">
         <v>849000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>264400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>359600</v>
       </c>
-      <c r="G9" s="3">
-        <v>806300</v>
-      </c>
       <c r="H9" s="3">
+        <v>784600</v>
+      </c>
+      <c r="I9" s="3">
         <v>842300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>276700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>427400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>850600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>986800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>354000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>407600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>880000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1000100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>420600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>475500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>883700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1084700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>447300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>609100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1114300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1158900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>548800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>673700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>954300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>829200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>311300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>405700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>747000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>716800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>261100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>350800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>635900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>604100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>187500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>288700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>590000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>621200</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>170600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>67400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>367100</v>
+      </c>
+      <c r="E10" s="3">
         <v>610500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>90000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>27700</v>
       </c>
-      <c r="G10" s="3">
-        <v>381700</v>
-      </c>
       <c r="H10" s="3">
+        <v>374700</v>
+      </c>
+      <c r="I10" s="3">
         <v>547400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>89900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-12700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>351600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>538600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>56400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-33100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>238700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>531400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>106000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>18200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>302400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>593700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>118700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>128700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>495400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>669900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>199800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>216600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>538400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>553600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>54500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>92000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>423300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>473100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>37000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>83100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>358700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>409200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>34000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>88000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>383400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>463400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>36800</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,130 +1244,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>-1500</v>
       </c>
-      <c r="G12" s="3">
-        <v>10200</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>-10600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>13600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>-26200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>13400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>11400</v>
-      </c>
-      <c r="X12" s="3">
-        <v>10300</v>
       </c>
       <c r="Y12" s="3">
         <v>10300</v>
       </c>
       <c r="Z12" s="3">
+        <v>10300</v>
+      </c>
+      <c r="AA12" s="3">
         <v>11700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>9200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>10800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>10200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>9400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>9200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>11800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>10500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>9400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>11200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>10100</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>9600</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>8900</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1475,189 +1492,195 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3100</v>
       </c>
-      <c r="F14" s="3">
-        <v>29000</v>
-      </c>
       <c r="G14" s="3">
-        <v>7500</v>
+        <v>38000</v>
       </c>
       <c r="H14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I14" s="3">
         <v>15700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>17900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>81300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>77000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-12900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>272400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>34500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>140500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>18800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>138100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>724200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>5400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>14900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>9700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>15900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>6000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>112300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>30400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>10200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>3600</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>400</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>1000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-200</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E15" s="3">
         <v>16100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>20000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>3500</v>
       </c>
       <c r="M15" s="3">
         <v>3500</v>
       </c>
       <c r="N15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="O15" s="3">
         <v>-18900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>7100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>8900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>7400</v>
-      </c>
-      <c r="V15" s="3">
-        <v>7300</v>
       </c>
       <c r="W15" s="3">
         <v>7300</v>
@@ -1669,58 +1692,61 @@
         <v>7300</v>
       </c>
       <c r="Z15" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AA15" s="3">
         <v>8400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>7700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>7900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>7500</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>8200</v>
       </c>
       <c r="AE15" s="3">
         <v>8200</v>
       </c>
       <c r="AF15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AG15" s="3">
         <v>8300</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>8200</v>
       </c>
       <c r="AH15" s="3">
         <v>8200</v>
       </c>
       <c r="AI15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>6700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>6600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>5800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>5300</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>5500</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>5300</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>974900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1055500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>373100</v>
       </c>
-      <c r="F17" s="3">
-        <v>510600</v>
-      </c>
       <c r="G17" s="3">
-        <v>956500</v>
+        <v>501600</v>
       </c>
       <c r="H17" s="3">
+        <v>936500</v>
+      </c>
+      <c r="I17" s="3">
         <v>1024300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>394500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>543500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>998300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1177600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>465800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>523000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1004000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1179500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>568400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>717600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1748600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1290500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>601400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>775000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1307600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1404700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>714600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>880700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1208200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1029100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>428400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>551600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>912100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>899700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>383000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>581100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>808900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>781000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>293400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>402800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>737300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>799300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>269200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>113200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>197200</v>
+      </c>
+      <c r="E18" s="3">
         <v>404000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-18700</v>
       </c>
-      <c r="F18" s="3">
-        <v>-123300</v>
-      </c>
       <c r="G18" s="3">
-        <v>231500</v>
+        <v>-114300</v>
       </c>
       <c r="H18" s="3">
+        <v>222800</v>
+      </c>
+      <c r="I18" s="3">
         <v>365400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-27900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-128800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>203900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>347800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-55400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-148500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>114700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>352000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-41800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-223900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-562500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>387900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-35400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-37200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>302100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>424100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>34000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>284500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>353700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-62600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-53900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>258200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>290200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-84900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-147200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>185700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>232300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-71900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-26100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>236100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>285300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-61800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>-40800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2048,353 +2081,360 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E20" s="3">
         <v>5600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>14300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>11500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-15100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="I20" s="3">
         <v>7100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>68900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-21600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>28900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>99700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-18900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>13400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-12700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>16800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>22700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>15200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>12800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-12500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>262300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>4100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-14700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-29900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-14600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-45600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-28500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>227500</v>
+      </c>
+      <c r="E21" s="3">
         <v>414500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-32300</v>
       </c>
-      <c r="F21" s="3">
-        <v>-116300</v>
-      </c>
       <c r="G21" s="3">
-        <v>265200</v>
+        <v>-107300</v>
       </c>
       <c r="H21" s="3">
+        <v>265400</v>
+      </c>
+      <c r="I21" s="3">
         <v>377300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-38400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-177700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>245900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>344400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-80800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-267100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>139600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>344300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-26400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-210200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-518600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>410100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-16000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-17700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>348300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>446900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>72300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>48100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>309500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>380000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-52700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>285600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>574900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-58500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-122300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>211200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>221800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-66800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-35700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>241400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>259500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-70200</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>-20900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E22" s="3">
         <v>31300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>26800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>31800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>36600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>33900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>33200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>38800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>44100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>42800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>40000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>47100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>48300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>42700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>35000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>31000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>28300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>16100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>22700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>22100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>25900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>29100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>25100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>21000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>23800</v>
-      </c>
-      <c r="AJ22" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AK22" s="3" t="s">
         <v>91</v>
@@ -2405,8 +2445,8 @@
       <c r="AM22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AN22" s="3">
-        <v>0</v>
+      <c r="AN22" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AO22" s="3">
         <v>0</v>
@@ -2414,252 +2454,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>155200</v>
+      </c>
+      <c r="E23" s="3">
         <v>364900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-63300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-190600</v>
       </c>
-      <c r="G23" s="3">
-        <v>207300</v>
-      </c>
       <c r="H23" s="3">
+        <v>214000</v>
+      </c>
+      <c r="I23" s="3">
         <v>306000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-90900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-312200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>183000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>219800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-114200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-560600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>52000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>149800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-94300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-271600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-576700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>355000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-64700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-63100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>302900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>404200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>33100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>266100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>333800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-95100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-73400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>237400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>523400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-105900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-165900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>166200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>202000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-86600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-56000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>221500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>239700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-90300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-40100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E24" s="3">
         <v>101600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-15500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-38700</v>
       </c>
-      <c r="G24" s="3">
-        <v>58200</v>
-      </c>
       <c r="H24" s="3">
+        <v>59300</v>
+      </c>
+      <c r="I24" s="3">
         <v>85300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-24800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-68200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>50900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-33700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-92200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>40400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-29600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-51600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-132800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>78500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-14700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-14400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>73100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>93100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>61800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>84000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-23800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-17800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>59400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>126500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-23300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-39500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>40700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>49300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-20800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-13700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>76900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>85600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-32200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-12700</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2780,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>103600</v>
+      </c>
+      <c r="E26" s="3">
         <v>263300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-47800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-151900</v>
       </c>
-      <c r="G26" s="3">
-        <v>149100</v>
-      </c>
       <c r="H26" s="3">
+        <v>154700</v>
+      </c>
+      <c r="I26" s="3">
         <v>220700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-66100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-244000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>132100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>157500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-80500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-468400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>43700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>109400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-64700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-220000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-443900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>276500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-50000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-48700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>229800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>311100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>25200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>204300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>249800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-71300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-55600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>178000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>396900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-82600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-126400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>125500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>152700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-65800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-42300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>144600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>154100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-58100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-27400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E27" s="3">
         <v>238600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-125000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-151900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>149100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>217500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-69500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-244000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>132100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>157500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-80500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-468400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>43700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>109400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-64700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-220000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-443900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>276500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-50000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-48700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>229800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>310900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>24400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>203800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>249600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-71400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-55300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>178100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>397000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-82500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-126500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>125600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>152600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-65800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-42300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>144600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>154000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-58500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-27100</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3146,32 +3204,35 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E29" s="3">
         <v>-24700</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-77200</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="I29" s="3">
         <v>-3200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-3400</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
@@ -3190,12 +3251,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -3206,70 +3267,73 @@
         <v>0</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>800</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-3900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-900</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>100</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>2600</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>23600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-500</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>2900</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-20500</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-42700</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>44600</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>8800</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>7300</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>11100</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-6800</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3390,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3512,252 +3579,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-14300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-11500</v>
       </c>
-      <c r="G32" s="3">
-        <v>15100</v>
-      </c>
       <c r="H32" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-7100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-68900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>21600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-28900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-99700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>18900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>12700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-16800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-22700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-15200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>12500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-262300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>30300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>14700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>29900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>14600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>45600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>28500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E33" s="3">
         <v>238600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-125000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-151900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>149100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>217500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-69500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-244000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>132100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>157500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-80500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-468400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>43700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>109400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-64700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-220000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-443900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>276500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-50000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-47900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>225900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>310000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>24400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>202800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>252200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-71400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-57900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>201700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>396500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-79600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-147000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>82900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>148900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-21200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-33500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>151900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>165100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-65300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3878,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E35" s="3">
         <v>238600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-125000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-151900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>149100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>217500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-69500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-244000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>132100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>157500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-80500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-468400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>43700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>109400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-64700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-220000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-443900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>276500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-50000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-47900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>225900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>310000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>24400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>202800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>252200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-71400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-57900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>201700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>396500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-79600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-147000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>82900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>148900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-21200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-33500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>151900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>165100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-65300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44562</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44198</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4171,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4215,130 +4301,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E41" s="3">
         <v>6200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>51100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>71600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>279900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>65100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>27400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>25000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>25600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>86800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>27800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>17100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>244100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>58300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>21500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>48300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>30800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>27400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>18800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>36400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>37500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>22600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>33900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>29600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>33000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>54500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>120500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>119100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>74300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>73100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>28600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -4349,41 +4439,41 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>16300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>12700</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4459,573 +4549,588 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E43" s="3">
         <v>766700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>193800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>186900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>573800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>799300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>213600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>176800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>504600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>876900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>287600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>304200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1159900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1457900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>490300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>378800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>952500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1434600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>415200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>483400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1058000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1408100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>497700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>497100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1147900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1172500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>236000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>308400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>746900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1032900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>208200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>310500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>704500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>931300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>170600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>286600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>752100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1121300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>175700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>301700</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>481400</v>
+      </c>
+      <c r="E44" s="3">
         <v>696000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>846700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>592800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>544300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>773200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>909800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>587500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>606800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>824300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1169600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>880300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>884900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1127600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1525900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1343500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1407600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1594100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1657200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1126600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>962800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1019200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1068300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>621900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>493100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>743300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>866100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>540300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>533700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>675300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>745400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>481400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>500500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>596900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>696100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>407500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>466600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>658500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>685900</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>394700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" s="3">
         <v>28500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>195100</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>700</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="N45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8800</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R45" s="3">
         <v>257500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>172800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>208600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>203800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>169900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>146900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>132000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>92000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>81000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>89500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>95800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>203300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>174200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>72900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>93700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>102500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>59900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>84400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>78100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>61700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>67100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>146500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>155500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>306500</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>430200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>1349100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1621900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1257200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>940300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1283300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1728600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1285400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>980400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1538400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1935100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1681400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1397800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2251000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2842400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2299300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1981900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2588700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3254400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2292600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2024000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2226000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2573700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1679500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1216600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1778800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2042400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1332800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1041700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1389900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1839400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1078700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>885700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1319000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1639300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>982900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>881700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1484300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2009600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1241200</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1032900</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E47" s="3">
         <v>36000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>40500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>78200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>65900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>40800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>48100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>91000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>115000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>93100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>97900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>177700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>209600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>185700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>181500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>193800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>208300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>193200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>199700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>207000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>224500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>201400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>202900</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -5037,284 +5142,293 @@
         <v>0</v>
       </c>
       <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
         <v>34500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>37300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>36100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>34400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>33200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>31700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>31100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>65700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>59900</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>83900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>101000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>977600</v>
+      </c>
+      <c r="E48" s="3">
         <v>911800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>896300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>887900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>873500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>863400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>867400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>874900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>875800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>881300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>893000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>872900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>856500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>844800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>885700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>894900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>905300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>914200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>910200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>915200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>795300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>773300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>730500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>716000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>663100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>661000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>674900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>546000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>506700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>513900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>519800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>530800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>517600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>463600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>464100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>467700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>460800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>460900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>438000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>444900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>594000</v>
+      </c>
+      <c r="E49" s="3">
         <v>594800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>595300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>645700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>653500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>655900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>658800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>662700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>668800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>672800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>677100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>680600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>814700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>819800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>830300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>834200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>881800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1488000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1493200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1314800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1224900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1221000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1234300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1223300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1225300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1230300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1242600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1246200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1373000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1377500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1386500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1400300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1500800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1244400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1248200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1190500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1215300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1187600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1131400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1435100</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5435,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5557,130 +5674,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>100200</v>
+      </c>
+      <c r="E52" s="3">
         <v>247500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>244700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>68800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>214400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>248000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>310500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>71600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>291300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>341900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>366700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>94900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>322600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>295400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>337200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>392000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>409600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>357700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>346500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>339000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>150400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>164700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>153500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>224600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>209600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>202000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>205700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>194800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>197800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>191200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>202900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>201600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>192100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>195000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>183900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>176000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>121400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>120400</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>117700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>115100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5801,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>3167400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3412000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3034000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2742000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3090600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3536700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3170200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2871900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3489300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3924200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3716100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3413700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4454400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4988100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4534000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4296800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4993700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6207500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5242200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4800000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4621100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4934100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4000700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3380500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3876800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4135700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3456000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3028700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3467400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3956500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3225200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3054500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3563900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3575500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2910800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2747000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>3347500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>3838400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>3012200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>2755800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5967,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -6011,740 +6141,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>310300</v>
+      </c>
+      <c r="E57" s="3">
         <v>385800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>292100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>229200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>261700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>396300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>309300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>254700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>316700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>440400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>332500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>271200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>365700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>415500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>366800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>422600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>291000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>507500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>427700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>609400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>467900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>549900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>498900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>391000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>310500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>324700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>309400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>214200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>222600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>298700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>237000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>150500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>195600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>253500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>223200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>153100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>224000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>322600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>218400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>336600</v>
+      </c>
+      <c r="E58" s="3">
         <v>340300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>344300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>128800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>125800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>130400</v>
       </c>
       <c r="I58" s="3">
         <v>130400</v>
       </c>
       <c r="J58" s="3">
+        <v>130400</v>
+      </c>
+      <c r="K58" s="3">
         <v>127900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>126800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>133700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>131700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>128700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>528400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>512800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>216800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>144300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>322000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>459700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>160700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>57800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>53700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>212800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>188000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>66400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>206400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>212200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>93800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>128100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>363200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>357700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>95100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>132600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>314500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>335800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>86100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>143100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>289100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>32100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>41800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>185000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>451900</v>
+      </c>
+      <c r="E59" s="3">
         <v>540700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>292600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>130300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>396300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>476500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>240200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>135100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>396900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>486200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>299900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>147700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>435000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>444200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>348100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>397000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>458900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>503100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>326800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>473200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>515200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>584800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>367600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>493000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>589800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>444300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>206500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>278200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>369600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>503500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>262500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>329600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>315200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>316800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>161800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>248300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>327400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>390000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>230400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>628900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>1110800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1275600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>932400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>739700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>798600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1012500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>683800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>750300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>854400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1060300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>764100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>773700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1329100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1372500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>931700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>963900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1071900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1470300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>915200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1140400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1036800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1347500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1054500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>950400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1106700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>981200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>609700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>620500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>955400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1159900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>594600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>612700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>825300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>906100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>471100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>544500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>840500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>744700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>490600</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>707100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>2153500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2325300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2497400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2251400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2348900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2701900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2848300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2390000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2666300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2984200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3205000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2777500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2845200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3341200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3189600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2826200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3155600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3350000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3082200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2236700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2132000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2322500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1979800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1455100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1516000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2113800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1969900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1523500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1563500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2039100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2186200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1883800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1975400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1937700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1697000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1258000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1419700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2055100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1648100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1030900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>111800</v>
+      </c>
+      <c r="E62" s="3">
         <v>97600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>104800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>36500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>114000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>112400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>117600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>42200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>114800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>130600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>132400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>52000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>145300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>136900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>353200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>359000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>348100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>412200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>413200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>409600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>329900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>323200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>287400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>272100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>250200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>246100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>247100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>161500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>143300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>135400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>191200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>198400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>231900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>235800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>234900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>282400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>344300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>347200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>281300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>597400</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6865,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6987,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7109,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>3376100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3698500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3534600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3099500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3261500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3826800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3649700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3262500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3635500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4175100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4101500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3681000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4319600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4850600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4474500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4149100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4575600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5232500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4410600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3786700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3498700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3993200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3328100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2683300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2878300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3346000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2831400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2310000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2667000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3339300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2976900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2699900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3037500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3084700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2408000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2097800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2617100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>3159500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2432400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2040600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7275,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7397,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7519,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7641,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7763,130 +7934,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>404300</v>
+      </c>
+      <c r="E72" s="3">
         <v>331000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>131200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>294700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>485200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>373700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>195800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>303800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>585800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>491800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>372400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>490900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>996800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>990300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>917900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1020100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1276900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1758800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1517800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1605100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1691000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1500200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1224400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1235600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1557000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1389000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1169800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1274700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1369300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1199200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>835400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>919900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1097500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1044500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>925900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>978200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1043100</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>921000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>786400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>881800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -8007,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8129,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8251,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>-208700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-286500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-500600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-357500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-170900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-290100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-479500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-390600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-146200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-250900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-385400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-267300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>134800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>137500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>59500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>147700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>418100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>975000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>831600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1013300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1122400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>940900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>672600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>697200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>998500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>789700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>624600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>718700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>800400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>617200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>248300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>354600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>526400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>490800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>502800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>648800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>730400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>678900</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>579800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>715200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8495,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44562</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44198</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E81" s="3">
         <v>238600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-125000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-151900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>149100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>217500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-69500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-244000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>132100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>157500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-80500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-468400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>43700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>109400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-64700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-220000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-443900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>276500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-50000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-47900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>225900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>310000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>24400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>202800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>252200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-71400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-57900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>201700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>396500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-79600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-147000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>82900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>148900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-21200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-33500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>151900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>165100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-65300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8788,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>15800</v>
+        <v>63900</v>
       </c>
       <c r="E83" s="3">
         <v>15800</v>
       </c>
       <c r="F83" s="3">
+        <v>15800</v>
+      </c>
+      <c r="G83" s="3">
         <v>-32200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>34000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>32700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-40800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>36100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>58900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-29000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>36400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>53300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>25200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>26400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>27100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>26800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>24900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>23800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>23500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>23400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>23100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>25700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>23100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>23500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>22400</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>22300</v>
       </c>
       <c r="AE83" s="3">
         <v>22300</v>
       </c>
       <c r="AF83" s="3">
+        <v>22300</v>
+      </c>
+      <c r="AG83" s="3">
         <v>22400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>22300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>22600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>21200</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>19800</v>
       </c>
       <c r="AK83" s="3">
         <v>19800</v>
       </c>
       <c r="AL83" s="3">
+        <v>19800</v>
+      </c>
+      <c r="AM83" s="3">
         <v>20300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>19900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>19800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>20100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9032,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9154,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9276,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9398,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9520,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>345600</v>
+      </c>
+      <c r="E89" s="3">
         <v>220000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-370400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>174100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>454400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>188100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-445300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>118500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>588000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>304200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-343200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>535300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>562600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-135300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-431600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>550600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>463000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-377500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-765100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>478600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>492800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-279200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-420700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>515500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>649600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-288900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-318200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>304500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>468400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-312700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-233400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>345900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>479400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-272300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-210500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>271600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>580600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-279200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-209800</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>266300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9686,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-42900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-29300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-37900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-29600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-33000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-46100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-29000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-34600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-21900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-7600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-19400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-27600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-16100</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-22600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9930,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10052,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-56700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-52100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-25300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-20400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-53200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-24000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>15400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-36000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>51300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-78700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-245200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-326700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-38100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-25600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-148200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-27500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>107800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-25700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>33800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>246800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-17100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-18400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-414400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-164800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>148800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-20300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-12100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-94000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-19600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10218,130 +10451,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E96" s="3">
         <v>39500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>38300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>38100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>38200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>38800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>39200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>37600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>37500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>38800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>37400</v>
-      </c>
-      <c r="N96" s="3">
-        <v>37100</v>
       </c>
       <c r="O96" s="3">
         <v>37100</v>
       </c>
       <c r="P96" s="3">
+        <v>37100</v>
+      </c>
+      <c r="Q96" s="3">
         <v>38300</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-36600</v>
       </c>
       <c r="R96" s="3">
         <v>-36600</v>
       </c>
       <c r="S96" s="3">
+        <v>-36600</v>
+      </c>
+      <c r="T96" s="3">
         <v>-36400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-56100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-37100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-36900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-35200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-36300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-34600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-313400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-32400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-33000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-32400</v>
       </c>
       <c r="AD96" s="3">
         <v>-32400</v>
       </c>
       <c r="AE96" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-30500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-31200</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-30400</v>
       </c>
       <c r="AH96" s="3">
         <v>-30400</v>
       </c>
       <c r="AI96" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-29300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-29800</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-30500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-30900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-29500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-29900</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-30000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-30200</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10462,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10584,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10706,370 +10949,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-270000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-198600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>366800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-135800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-396100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-169800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>407700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-306800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-363900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-231400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>374200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-509100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-536300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>119100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>406200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-542600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-373400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>388700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>782600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>34400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-411500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>297600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>573500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-519700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-624700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>185000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>352300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-313600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-503500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>80700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>239900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-324600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-137100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>304200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>308700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-418600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-518800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>284600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>345200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-275000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>200</v>
       </c>
       <c r="M101" s="3">
         <v>200</v>
       </c>
       <c r="N101" s="3">
+        <v>200</v>
+      </c>
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>3700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-25300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>34200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-61800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-208300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>214800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>54700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-61200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>59000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>10700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-227700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>185800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>43900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-31700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>17500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>8600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-17600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>14900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-11300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-21500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-66000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>44800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-14400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>38600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-27100</v>
       </c>
     </row>
